--- a/从零开始学Slots/从零开始学Slots-10-数值篇-Scatter(2).xlsx
+++ b/从零开始学Slots/从零开始学Slots-10-数值篇-Scatter(2).xlsx
@@ -5683,6 +5683,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:K113" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -6124,5 +6127,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M54" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-10-数值篇-Scatter(2).xlsx
+++ b/从零开始学Slots/从零开始学Slots-10-数值篇-Scatter(2).xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
   <si>
     <r>
       <rPr>
@@ -4864,7 +4864,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4983,6 +4983,18 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -5768,11 +5780,11 @@
       <c r="A7" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>88</v>
+      <c r="B7" s="30">
+        <v>5</v>
+      </c>
+      <c r="C7" s="31">
+        <v>5</v>
       </c>
       <c r="D7" s="16"/>
       <c r="E7" s="16"/>
@@ -5913,8 +5925,8 @@
       <c r="C20" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="D20" s="22" t="s">
-        <v>107</v>
+      <c r="D20" s="32">
+        <v>17</v>
       </c>
       <c r="E20" s="13" t="s">
         <v>108</v>

--- a/从零开始学Slots/从零开始学Slots-10-数值篇-Scatter(2).xlsx
+++ b/从零开始学Slots/从零开始学Slots-10-数值篇-Scatter(2).xlsx
@@ -4684,10 +4684,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0000%"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -4864,7 +4865,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4995,6 +4996,14 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" applyNumberFormat="1" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" applyNumberFormat="1" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -5845,7 +5854,7 @@
       <c r="A13" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="33" t="n">
         <f aca="false">3/16</f>
         <v>0.1875</v>
       </c>
@@ -5890,7 +5899,7 @@
       <c r="A17" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="B17" s="21" t="n">
+      <c r="B17" s="34" t="n">
         <f aca="false">BINOMDIST(B15,B12,B13,TRUE())-BINOMDIST(B14-1,B12,B13,TRUE())</f>
         <v>0.0487689971923829</v>
       </c>
@@ -5936,7 +5945,7 @@
       <c r="A21" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B21" s="18" t="n">
+      <c r="B21" s="33" t="n">
         <f aca="false">BINOMDIST(A21,$B$12,$B$13,FALSE())</f>
         <v>0.0435161590576172</v>
       </c>
@@ -5956,7 +5965,7 @@
       <c r="A22" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B22" s="18" t="n">
+      <c r="B22" s="33" t="n">
         <f aca="false">BINOMDIST(A22,$B$12,$B$13,FALSE())</f>
         <v>0.00502109527587891</v>
       </c>
@@ -5976,7 +5985,7 @@
       <c r="A23" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B23" s="18" t="n">
+      <c r="B23" s="33" t="n">
         <f aca="false">BINOMDIST(A23,$B$12,$B$13,FALSE())</f>
         <v>0.000231742858886719</v>
       </c>
@@ -5996,7 +6005,7 @@
       <c r="A24" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="B24" s="21" t="n">
+      <c r="B24" s="34" t="n">
         <f aca="false">SUM(B21:B23)</f>
         <v>0.0487689971923828</v>
       </c>
